--- a/Hoàng/2025/T5/CÔNG TY TIN HỌC MỸ VIỆT (81-2025)/Báo giá - Công ty Tin Học Mỹ Việt.xlsx
+++ b/Hoàng/2025/T5/CÔNG TY TIN HỌC MỸ VIỆT (81-2025)/Báo giá - Công ty Tin Học Mỹ Việt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CÔNG TY TIN HỌC MỸ VIỆT (81-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08430FB-ECA5-4F6D-AF80-105FAAD61B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13515B0D-008F-45A6-8840-9900B1769288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="597" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2316,6 +2316,141 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2360,141 +2495,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2890,48 +2890,48 @@
       <c r="A1" s="6"/>
       <c r="B1" s="135"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="170" t="s">
+      <c r="D1" s="177" t="s">
         <v>330</v>
       </c>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="172"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="136"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="172"/>
+      <c r="D2" s="177"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="179"/>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="136"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="172"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="136"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="171"/>
-      <c r="F4" s="171"/>
-      <c r="G4" s="172"/>
+      <c r="D4" s="177"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="179"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="136"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="175"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="182"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -2939,21 +2939,21 @@
       </c>
       <c r="B6" s="137"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="178"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="185"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="180"/>
-      <c r="C7" s="180"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="181"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="188"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -2971,40 +2971,40 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="157" t="s">
+      <c r="A9" s="202" t="s">
         <v>418</v>
       </c>
-      <c r="B9" s="158"/>
-      <c r="C9" s="158"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="159"/>
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="204"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
     </row>
     <row r="10" spans="1:10" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="205" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="161"/>
-      <c r="C10" s="161"/>
-      <c r="D10" s="161"/>
-      <c r="E10" s="161"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="162"/>
+      <c r="B10" s="206"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="207"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
     </row>
     <row r="11" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="163"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="A11" s="208"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="209"/>
+      <c r="F11" s="209"/>
+      <c r="G11" s="210"/>
       <c r="H11" s="24"/>
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
@@ -3023,10 +3023,10 @@
       <c r="A13" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="201" t="s">
+      <c r="B13" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="201"/>
+      <c r="C13" s="159"/>
       <c r="D13" s="36" t="s">
         <v>3</v>
       </c>
@@ -3042,12 +3042,12 @@
       <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="202" t="s">
+      <c r="A14" s="160" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
+      <c r="B14" s="160"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
       <c r="E14" s="12"/>
       <c r="F14" s="39"/>
       <c r="G14" s="118"/>
@@ -3057,92 +3057,92 @@
       <c r="A15" s="37">
         <v>1</v>
       </c>
-      <c r="B15" s="191" t="s">
+      <c r="B15" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="203" t="s">
+      <c r="C15" s="161" t="s">
         <v>60</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="200">
+      <c r="E15" s="158">
         <v>200000</v>
       </c>
-      <c r="F15" s="199">
+      <c r="F15" s="157">
         <v>150000</v>
       </c>
-      <c r="G15" s="182"/>
+      <c r="G15" s="189"/>
       <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2</v>
       </c>
-      <c r="B16" s="191"/>
-      <c r="C16" s="203"/>
+      <c r="B16" s="162"/>
+      <c r="C16" s="161"/>
       <c r="D16" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="200"/>
-      <c r="F16" s="199"/>
-      <c r="G16" s="182"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="189"/>
       <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>3</v>
       </c>
-      <c r="B17" s="191"/>
-      <c r="C17" s="203"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="200"/>
-      <c r="F17" s="199"/>
-      <c r="G17" s="182"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="189"/>
       <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>4</v>
       </c>
-      <c r="B18" s="191"/>
-      <c r="C18" s="203"/>
+      <c r="B18" s="162"/>
+      <c r="C18" s="161"/>
       <c r="D18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="199"/>
-      <c r="G18" s="182"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="189"/>
       <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>5</v>
       </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="203"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="161"/>
       <c r="D19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="200"/>
-      <c r="F19" s="199"/>
-      <c r="G19" s="182"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="189"/>
       <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>6</v>
       </c>
-      <c r="B20" s="191"/>
-      <c r="C20" s="203"/>
+      <c r="B20" s="162"/>
+      <c r="C20" s="161"/>
       <c r="D20" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="200"/>
-      <c r="F20" s="199"/>
-      <c r="G20" s="182"/>
+      <c r="E20" s="158"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="189"/>
       <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="33" x14ac:dyDescent="0.25">
@@ -3241,7 +3241,7 @@
       <c r="A25" s="37">
         <v>14</v>
       </c>
-      <c r="B25" s="191" t="s">
+      <c r="B25" s="162" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="14" t="s">
@@ -3264,7 +3264,7 @@
       <c r="A26" s="37">
         <v>15</v>
       </c>
-      <c r="B26" s="191"/>
+      <c r="B26" s="162"/>
       <c r="C26" s="14" t="s">
         <v>38</v>
       </c>
@@ -3327,10 +3327,10 @@
       <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="195">
+      <c r="A29" s="165">
         <v>18</v>
       </c>
-      <c r="B29" s="196"/>
+      <c r="B29" s="166"/>
       <c r="C29" s="19" t="s">
         <v>22</v>
       </c>
@@ -3346,9 +3346,9 @@
       <c r="G29" s="119"/>
       <c r="H29" s="41"/>
     </row>
-    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="195"/>
-      <c r="B30" s="196"/>
+    <row r="30" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="165"/>
+      <c r="B30" s="166"/>
       <c r="C30" s="19" t="s">
         <v>42</v>
       </c>
@@ -3363,12 +3363,12 @@
       <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:8" s="47" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="194" t="s">
+      <c r="A31" s="170" t="s">
         <v>326</v>
       </c>
-      <c r="B31" s="194"/>
-      <c r="C31" s="194"/>
-      <c r="D31" s="194"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="170"/>
       <c r="E31" s="112">
         <f>SUM(E15:E30)</f>
         <v>729000</v>
@@ -3413,10 +3413,10 @@
       <c r="A35" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="190" t="s">
+      <c r="B35" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="190"/>
+      <c r="C35" s="163"/>
       <c r="D35" s="59" t="s">
         <v>3</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="E37" s="62">
         <v>169000</v>
       </c>
-      <c r="F37" s="206">
+      <c r="F37" s="151">
         <f>E37*0.9</f>
         <v>152100</v>
       </c>
@@ -3482,7 +3482,7 @@
       <c r="E38" s="62">
         <v>41000</v>
       </c>
-      <c r="F38" s="206">
+      <c r="F38" s="151">
         <f t="shared" ref="F38:F101" si="1">E38*0.9</f>
         <v>36900</v>
       </c>
@@ -3505,7 +3505,7 @@
       <c r="E39" s="65">
         <v>41000</v>
       </c>
-      <c r="F39" s="206">
+      <c r="F39" s="151">
         <f t="shared" si="1"/>
         <v>36900</v>
       </c>
@@ -3528,7 +3528,7 @@
       <c r="E40" s="65">
         <v>47000</v>
       </c>
-      <c r="F40" s="206">
+      <c r="F40" s="151">
         <f t="shared" si="1"/>
         <v>42300</v>
       </c>
@@ -3539,7 +3539,7 @@
       <c r="A41" s="61">
         <v>5</v>
       </c>
-      <c r="B41" s="168" t="s">
+      <c r="B41" s="164" t="s">
         <v>39</v>
       </c>
       <c r="C41" s="64" t="s">
@@ -3551,7 +3551,7 @@
       <c r="E41" s="65">
         <v>41000</v>
       </c>
-      <c r="F41" s="206">
+      <c r="F41" s="151">
         <f t="shared" si="1"/>
         <v>36900</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="A42" s="61">
         <v>6</v>
       </c>
-      <c r="B42" s="168"/>
+      <c r="B42" s="164"/>
       <c r="C42" s="64" t="s">
         <v>101</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="E42" s="65">
         <v>41000</v>
       </c>
-      <c r="F42" s="206">
+      <c r="F42" s="151">
         <f t="shared" si="1"/>
         <v>36900</v>
       </c>
@@ -3587,7 +3587,7 @@
       <c r="A43" s="61">
         <v>7</v>
       </c>
-      <c r="B43" s="169" t="s">
+      <c r="B43" s="171" t="s">
         <v>341</v>
       </c>
       <c r="C43" s="64" t="s">
@@ -3599,11 +3599,11 @@
       <c r="E43" s="65">
         <v>41000</v>
       </c>
-      <c r="F43" s="206">
+      <c r="F43" s="151">
         <f t="shared" si="1"/>
         <v>36900</v>
       </c>
-      <c r="G43" s="168" t="s">
+      <c r="G43" s="164" t="s">
         <v>342</v>
       </c>
       <c r="H43" s="41"/>
@@ -3612,7 +3612,7 @@
       <c r="A44" s="61">
         <v>8</v>
       </c>
-      <c r="B44" s="169"/>
+      <c r="B44" s="171"/>
       <c r="C44" s="64" t="s">
         <v>47</v>
       </c>
@@ -3622,18 +3622,18 @@
       <c r="E44" s="65">
         <v>59000</v>
       </c>
-      <c r="F44" s="206">
+      <c r="F44" s="151">
         <f t="shared" si="1"/>
         <v>53100</v>
       </c>
-      <c r="G44" s="168"/>
+      <c r="G44" s="164"/>
       <c r="H44" s="41"/>
     </row>
     <row r="45" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="61">
         <v>9</v>
       </c>
-      <c r="B45" s="169"/>
+      <c r="B45" s="171"/>
       <c r="C45" s="64" t="s">
         <v>343</v>
       </c>
@@ -3643,18 +3643,18 @@
       <c r="E45" s="65">
         <v>59000</v>
       </c>
-      <c r="F45" s="206">
+      <c r="F45" s="151">
         <f t="shared" si="1"/>
         <v>53100</v>
       </c>
-      <c r="G45" s="168"/>
+      <c r="G45" s="164"/>
       <c r="H45" s="41"/>
     </row>
     <row r="46" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="61">
         <v>10</v>
       </c>
-      <c r="B46" s="169"/>
+      <c r="B46" s="171"/>
       <c r="C46" s="64" t="s">
         <v>49</v>
       </c>
@@ -3664,18 +3664,18 @@
       <c r="E46" s="65">
         <v>47000</v>
       </c>
-      <c r="F46" s="206">
+      <c r="F46" s="151">
         <f t="shared" si="1"/>
         <v>42300</v>
       </c>
-      <c r="G46" s="168"/>
+      <c r="G46" s="164"/>
       <c r="H46" s="41"/>
     </row>
     <row r="47" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="61">
         <v>11</v>
       </c>
-      <c r="B47" s="169"/>
+      <c r="B47" s="171"/>
       <c r="C47" s="64" t="s">
         <v>51</v>
       </c>
@@ -3685,11 +3685,11 @@
       <c r="E47" s="65">
         <v>41000</v>
       </c>
-      <c r="F47" s="206">
+      <c r="F47" s="151">
         <f t="shared" si="1"/>
         <v>36900</v>
       </c>
-      <c r="G47" s="168"/>
+      <c r="G47" s="164"/>
       <c r="H47" s="41"/>
     </row>
     <row r="48" spans="1:8" ht="33" x14ac:dyDescent="0.25">
@@ -3708,7 +3708,7 @@
       <c r="E48" s="66">
         <v>102000</v>
       </c>
-      <c r="F48" s="206">
+      <c r="F48" s="151">
         <f t="shared" si="1"/>
         <v>91800</v>
       </c>
@@ -3719,7 +3719,7 @@
       <c r="A49" s="61">
         <v>13</v>
       </c>
-      <c r="B49" s="168" t="s">
+      <c r="B49" s="164" t="s">
         <v>345</v>
       </c>
       <c r="C49" s="26" t="s">
@@ -3731,11 +3731,11 @@
       <c r="E49" s="66">
         <v>62000</v>
       </c>
-      <c r="F49" s="206">
+      <c r="F49" s="151">
         <f t="shared" si="1"/>
         <v>55800</v>
       </c>
-      <c r="G49" s="168" t="s">
+      <c r="G49" s="164" t="s">
         <v>348</v>
       </c>
       <c r="H49" s="41"/>
@@ -3744,7 +3744,7 @@
       <c r="A50" s="61">
         <v>14</v>
       </c>
-      <c r="B50" s="168"/>
+      <c r="B50" s="164"/>
       <c r="C50" s="26" t="s">
         <v>349</v>
       </c>
@@ -3754,18 +3754,18 @@
       <c r="E50" s="66">
         <v>165000</v>
       </c>
-      <c r="F50" s="206">
+      <c r="F50" s="151">
         <f>E50*0.9</f>
         <v>148500</v>
       </c>
-      <c r="G50" s="168"/>
+      <c r="G50" s="164"/>
       <c r="H50" s="41"/>
     </row>
     <row r="51" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A51" s="61">
         <v>15</v>
       </c>
-      <c r="B51" s="168"/>
+      <c r="B51" s="164"/>
       <c r="C51" s="26" t="s">
         <v>351</v>
       </c>
@@ -3775,18 +3775,18 @@
       <c r="E51" s="66">
         <v>116000</v>
       </c>
-      <c r="F51" s="206">
+      <c r="F51" s="151">
         <f t="shared" si="1"/>
         <v>104400</v>
       </c>
-      <c r="G51" s="168"/>
+      <c r="G51" s="164"/>
       <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="61">
         <v>16</v>
       </c>
-      <c r="B52" s="168" t="s">
+      <c r="B52" s="164" t="s">
         <v>106</v>
       </c>
       <c r="C52" s="26" t="s">
@@ -3798,7 +3798,7 @@
       <c r="E52" s="66">
         <v>83000</v>
       </c>
-      <c r="F52" s="206">
+      <c r="F52" s="151">
         <f t="shared" si="1"/>
         <v>74700</v>
       </c>
@@ -3809,7 +3809,7 @@
       <c r="A53" s="61">
         <v>17</v>
       </c>
-      <c r="B53" s="168"/>
+      <c r="B53" s="164"/>
       <c r="C53" s="26" t="s">
         <v>353</v>
       </c>
@@ -3819,11 +3819,11 @@
       <c r="E53" s="66">
         <v>130000</v>
       </c>
-      <c r="F53" s="206">
+      <c r="F53" s="151">
         <f t="shared" si="1"/>
         <v>117000</v>
       </c>
-      <c r="G53" s="168" t="s">
+      <c r="G53" s="164" t="s">
         <v>348</v>
       </c>
       <c r="H53" s="41"/>
@@ -3832,7 +3832,7 @@
       <c r="A54" s="61">
         <v>18</v>
       </c>
-      <c r="B54" s="168"/>
+      <c r="B54" s="164"/>
       <c r="C54" s="26" t="s">
         <v>354</v>
       </c>
@@ -3842,18 +3842,18 @@
       <c r="E54" s="66">
         <v>120000</v>
       </c>
-      <c r="F54" s="206">
+      <c r="F54" s="151">
         <f t="shared" si="1"/>
         <v>108000</v>
       </c>
-      <c r="G54" s="168"/>
+      <c r="G54" s="164"/>
       <c r="H54" s="41"/>
     </row>
     <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="61">
         <v>19</v>
       </c>
-      <c r="B55" s="168"/>
+      <c r="B55" s="164"/>
       <c r="C55" s="26" t="s">
         <v>355</v>
       </c>
@@ -3863,11 +3863,11 @@
       <c r="E55" s="66">
         <v>282000</v>
       </c>
-      <c r="F55" s="206">
+      <c r="F55" s="151">
         <f t="shared" si="1"/>
         <v>253800</v>
       </c>
-      <c r="G55" s="168"/>
+      <c r="G55" s="164"/>
       <c r="H55" s="41"/>
     </row>
     <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
       <c r="E56" s="66">
         <v>128000</v>
       </c>
-      <c r="F56" s="206">
+      <c r="F56" s="151">
         <f t="shared" si="1"/>
         <v>115200</v>
       </c>
@@ -3897,7 +3897,7 @@
       <c r="A57" s="61">
         <v>21</v>
       </c>
-      <c r="B57" s="169" t="s">
+      <c r="B57" s="171" t="s">
         <v>109</v>
       </c>
       <c r="C57" s="26" t="s">
@@ -3909,11 +3909,11 @@
       <c r="E57" s="66">
         <v>71000</v>
       </c>
-      <c r="F57" s="206">
+      <c r="F57" s="151">
         <f t="shared" si="1"/>
         <v>63900</v>
       </c>
-      <c r="G57" s="168" t="s">
+      <c r="G57" s="164" t="s">
         <v>357</v>
       </c>
       <c r="H57" s="41"/>
@@ -3922,7 +3922,7 @@
       <c r="A58" s="61">
         <v>22</v>
       </c>
-      <c r="B58" s="169"/>
+      <c r="B58" s="171"/>
       <c r="C58" s="26" t="s">
         <v>112</v>
       </c>
@@ -3932,11 +3932,11 @@
       <c r="E58" s="62">
         <v>138000</v>
       </c>
-      <c r="F58" s="206">
+      <c r="F58" s="151">
         <f t="shared" si="1"/>
         <v>124200</v>
       </c>
-      <c r="G58" s="168"/>
+      <c r="G58" s="164"/>
       <c r="H58" s="41"/>
     </row>
     <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -3955,7 +3955,7 @@
       <c r="E59" s="62">
         <v>282000</v>
       </c>
-      <c r="F59" s="206">
+      <c r="F59" s="151">
         <f t="shared" si="1"/>
         <v>253800</v>
       </c>
@@ -3966,7 +3966,7 @@
       <c r="A60" s="61">
         <v>24</v>
       </c>
-      <c r="B60" s="168" t="s">
+      <c r="B60" s="164" t="s">
         <v>117</v>
       </c>
       <c r="C60" s="26" t="s">
@@ -3978,11 +3978,11 @@
       <c r="E60" s="66">
         <v>30000</v>
       </c>
-      <c r="F60" s="206">
+      <c r="F60" s="151">
         <f t="shared" si="1"/>
         <v>27000</v>
       </c>
-      <c r="G60" s="189" t="s">
+      <c r="G60" s="167" t="s">
         <v>358</v>
       </c>
       <c r="H60" s="46"/>
@@ -3991,7 +3991,7 @@
       <c r="A61" s="61">
         <v>25</v>
       </c>
-      <c r="B61" s="168"/>
+      <c r="B61" s="164"/>
       <c r="C61" s="26" t="s">
         <v>120</v>
       </c>
@@ -4001,20 +4001,20 @@
       <c r="E61" s="66">
         <v>20000</v>
       </c>
-      <c r="F61" s="206">
+      <c r="F61" s="151">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="G61" s="189"/>
+      <c r="G61" s="167"/>
       <c r="H61" s="46"/>
     </row>
     <row r="62" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="166" t="s">
+      <c r="A62" s="175" t="s">
         <v>359</v>
       </c>
-      <c r="B62" s="166"/>
-      <c r="C62" s="166"/>
-      <c r="D62" s="166"/>
+      <c r="B62" s="175"/>
+      <c r="C62" s="175"/>
+      <c r="D62" s="175"/>
       <c r="E62" s="107"/>
       <c r="F62" s="107"/>
       <c r="G62" s="126"/>
@@ -4024,7 +4024,7 @@
       <c r="A63" s="61">
         <v>26</v>
       </c>
-      <c r="B63" s="168" t="s">
+      <c r="B63" s="164" t="s">
         <v>85</v>
       </c>
       <c r="C63" s="25" t="s">
@@ -4036,7 +4036,7 @@
       <c r="E63" s="67">
         <v>174000</v>
       </c>
-      <c r="F63" s="206">
+      <c r="F63" s="151">
         <f t="shared" si="1"/>
         <v>156600</v>
       </c>
@@ -4047,7 +4047,7 @@
       <c r="A64" s="61">
         <v>27</v>
       </c>
-      <c r="B64" s="168"/>
+      <c r="B64" s="164"/>
       <c r="C64" s="25" t="s">
         <v>121</v>
       </c>
@@ -4057,7 +4057,7 @@
       <c r="E64" s="67">
         <v>231000</v>
       </c>
-      <c r="F64" s="206">
+      <c r="F64" s="151">
         <f t="shared" si="1"/>
         <v>207900</v>
       </c>
@@ -4068,7 +4068,7 @@
       <c r="A65" s="61">
         <v>28</v>
       </c>
-      <c r="B65" s="168"/>
+      <c r="B65" s="164"/>
       <c r="C65" s="25" t="s">
         <v>123</v>
       </c>
@@ -4078,7 +4078,7 @@
       <c r="E65" s="67">
         <v>732000</v>
       </c>
-      <c r="F65" s="206">
+      <c r="F65" s="151">
         <f t="shared" si="1"/>
         <v>658800</v>
       </c>
@@ -4089,7 +4089,7 @@
       <c r="A66" s="61">
         <v>29</v>
       </c>
-      <c r="B66" s="168"/>
+      <c r="B66" s="164"/>
       <c r="C66" s="25" t="s">
         <v>70</v>
       </c>
@@ -4099,7 +4099,7 @@
       <c r="E66" s="68">
         <v>121000</v>
       </c>
-      <c r="F66" s="206">
+      <c r="F66" s="151">
         <f t="shared" si="1"/>
         <v>108900</v>
       </c>
@@ -4110,7 +4110,7 @@
       <c r="A67" s="61">
         <v>30</v>
       </c>
-      <c r="B67" s="168"/>
+      <c r="B67" s="164"/>
       <c r="C67" s="25" t="s">
         <v>125</v>
       </c>
@@ -4120,7 +4120,7 @@
       <c r="E67" s="67">
         <v>192000</v>
       </c>
-      <c r="F67" s="206">
+      <c r="F67" s="151">
         <f t="shared" si="1"/>
         <v>172800</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="A68" s="61">
         <v>31</v>
       </c>
-      <c r="B68" s="168"/>
+      <c r="B68" s="164"/>
       <c r="C68" s="25" t="s">
         <v>74</v>
       </c>
@@ -4141,7 +4141,7 @@
       <c r="E68" s="67">
         <v>173000</v>
       </c>
-      <c r="F68" s="206">
+      <c r="F68" s="151">
         <f t="shared" si="1"/>
         <v>155700</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="A69" s="61">
         <v>32</v>
       </c>
-      <c r="B69" s="168"/>
+      <c r="B69" s="164"/>
       <c r="C69" s="25" t="s">
         <v>127</v>
       </c>
@@ -4162,7 +4162,7 @@
       <c r="E69" s="67">
         <v>231000</v>
       </c>
-      <c r="F69" s="206">
+      <c r="F69" s="151">
         <f t="shared" si="1"/>
         <v>207900</v>
       </c>
@@ -4175,7 +4175,7 @@
       <c r="A70" s="61">
         <v>33</v>
       </c>
-      <c r="B70" s="168"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="27" t="s">
         <v>129</v>
       </c>
@@ -4185,7 +4185,7 @@
       <c r="E70" s="69">
         <v>500000</v>
       </c>
-      <c r="F70" s="206">
+      <c r="F70" s="151">
         <f t="shared" si="1"/>
         <v>450000</v>
       </c>
@@ -4196,7 +4196,7 @@
       <c r="A71" s="61">
         <v>34</v>
       </c>
-      <c r="B71" s="168"/>
+      <c r="B71" s="164"/>
       <c r="C71" s="25" t="s">
         <v>72</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="E71" s="67">
         <v>290000</v>
       </c>
-      <c r="F71" s="206">
+      <c r="F71" s="151">
         <f t="shared" si="1"/>
         <v>261000</v>
       </c>
@@ -4219,7 +4219,7 @@
       <c r="A72" s="61">
         <v>35</v>
       </c>
-      <c r="B72" s="168"/>
+      <c r="B72" s="164"/>
       <c r="C72" s="25" t="s">
         <v>131</v>
       </c>
@@ -4229,7 +4229,7 @@
       <c r="E72" s="67">
         <v>231000</v>
       </c>
-      <c r="F72" s="206">
+      <c r="F72" s="151">
         <f t="shared" si="1"/>
         <v>207900</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="A73" s="61">
         <v>36</v>
       </c>
-      <c r="B73" s="168"/>
+      <c r="B73" s="164"/>
       <c r="C73" s="25" t="s">
         <v>133</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="E73" s="67">
         <v>616000</v>
       </c>
-      <c r="F73" s="206">
+      <c r="F73" s="151">
         <f t="shared" si="1"/>
         <v>554400</v>
       </c>
@@ -4261,7 +4261,7 @@
       <c r="A74" s="61">
         <v>37</v>
       </c>
-      <c r="B74" s="168"/>
+      <c r="B74" s="164"/>
       <c r="C74" s="25" t="s">
         <v>135</v>
       </c>
@@ -4271,7 +4271,7 @@
       <c r="E74" s="67">
         <v>231000</v>
       </c>
-      <c r="F74" s="206">
+      <c r="F74" s="151">
         <f t="shared" si="1"/>
         <v>207900</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="A75" s="61">
         <v>38</v>
       </c>
-      <c r="B75" s="168"/>
+      <c r="B75" s="164"/>
       <c r="C75" s="25" t="s">
         <v>137</v>
       </c>
@@ -4292,7 +4292,7 @@
       <c r="E75" s="67">
         <v>412000</v>
       </c>
-      <c r="F75" s="206">
+      <c r="F75" s="151">
         <f t="shared" si="1"/>
         <v>370800</v>
       </c>
@@ -4303,23 +4303,23 @@
       <c r="A76" s="61">
         <v>39</v>
       </c>
-      <c r="B76" s="168" t="s">
+      <c r="B76" s="164" t="s">
         <v>65</v>
       </c>
       <c r="C76" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D76" s="188" t="s">
+      <c r="D76" s="172" t="s">
         <v>67</v>
       </c>
       <c r="E76" s="67">
         <v>137000</v>
       </c>
-      <c r="F76" s="206">
+      <c r="F76" s="151">
         <f t="shared" si="1"/>
         <v>123300</v>
       </c>
-      <c r="G76" s="168" t="s">
+      <c r="G76" s="164" t="s">
         <v>415</v>
       </c>
       <c r="H76" s="46"/>
@@ -4328,57 +4328,57 @@
       <c r="A77" s="61">
         <v>40</v>
       </c>
-      <c r="B77" s="168"/>
+      <c r="B77" s="164"/>
       <c r="C77" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D77" s="188"/>
+      <c r="D77" s="172"/>
       <c r="E77" s="67">
         <v>137000</v>
       </c>
-      <c r="F77" s="206">
+      <c r="F77" s="151">
         <f t="shared" si="1"/>
         <v>123300</v>
       </c>
-      <c r="G77" s="168"/>
+      <c r="G77" s="164"/>
       <c r="H77" s="46"/>
     </row>
     <row r="78" spans="1:8" s="47" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="61">
         <v>41</v>
       </c>
-      <c r="B78" s="168"/>
+      <c r="B78" s="164"/>
       <c r="C78" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D78" s="188"/>
+      <c r="D78" s="172"/>
       <c r="E78" s="67">
         <v>208000</v>
       </c>
-      <c r="F78" s="206">
+      <c r="F78" s="151">
         <f t="shared" si="1"/>
         <v>187200</v>
       </c>
-      <c r="G78" s="168"/>
+      <c r="G78" s="164"/>
       <c r="H78" s="46"/>
     </row>
     <row r="79" spans="1:8" s="47" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A79" s="61">
         <v>42</v>
       </c>
-      <c r="B79" s="168" t="s">
+      <c r="B79" s="164" t="s">
         <v>139</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="D79" s="188" t="s">
+      <c r="D79" s="172" t="s">
         <v>141</v>
       </c>
       <c r="E79" s="67">
         <v>215000</v>
       </c>
-      <c r="F79" s="206">
+      <c r="F79" s="151">
         <f t="shared" si="1"/>
         <v>193500</v>
       </c>
@@ -4389,15 +4389,15 @@
       <c r="A80" s="61">
         <v>43</v>
       </c>
-      <c r="B80" s="168"/>
+      <c r="B80" s="164"/>
       <c r="C80" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="188"/>
+      <c r="D80" s="172"/>
       <c r="E80" s="67">
         <v>323000</v>
       </c>
-      <c r="F80" s="206">
+      <c r="F80" s="151">
         <f t="shared" si="1"/>
         <v>290700</v>
       </c>
@@ -4408,7 +4408,7 @@
       <c r="A81" s="61">
         <v>44</v>
       </c>
-      <c r="B81" s="168"/>
+      <c r="B81" s="164"/>
       <c r="C81" s="25" t="s">
         <v>143</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="E81" s="67">
         <v>269000</v>
       </c>
-      <c r="F81" s="206">
+      <c r="F81" s="151">
         <f t="shared" si="1"/>
         <v>242100</v>
       </c>
@@ -4429,7 +4429,7 @@
       <c r="A82" s="61">
         <v>45</v>
       </c>
-      <c r="B82" s="168"/>
+      <c r="B82" s="164"/>
       <c r="C82" s="25" t="s">
         <v>145</v>
       </c>
@@ -4439,7 +4439,7 @@
       <c r="E82" s="67">
         <v>588000</v>
       </c>
-      <c r="F82" s="206">
+      <c r="F82" s="151">
         <f t="shared" si="1"/>
         <v>529200</v>
       </c>
@@ -4447,12 +4447,12 @@
       <c r="H82" s="46"/>
     </row>
     <row r="83" spans="1:8" s="47" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="166" t="s">
+      <c r="A83" s="175" t="s">
         <v>362</v>
       </c>
-      <c r="B83" s="166"/>
-      <c r="C83" s="166"/>
-      <c r="D83" s="166"/>
+      <c r="B83" s="175"/>
+      <c r="C83" s="175"/>
+      <c r="D83" s="175"/>
       <c r="E83" s="107"/>
       <c r="F83" s="107"/>
       <c r="G83" s="126"/>
@@ -4462,7 +4462,7 @@
       <c r="A84" s="61">
         <v>46</v>
       </c>
-      <c r="B84" s="169" t="s">
+      <c r="B84" s="171" t="s">
         <v>147</v>
       </c>
       <c r="C84" s="26" t="s">
@@ -4474,7 +4474,7 @@
       <c r="E84" s="66">
         <v>123000</v>
       </c>
-      <c r="F84" s="206">
+      <c r="F84" s="151">
         <f t="shared" si="1"/>
         <v>110700</v>
       </c>
@@ -4485,7 +4485,7 @@
       <c r="A85" s="61">
         <v>47</v>
       </c>
-      <c r="B85" s="169"/>
+      <c r="B85" s="171"/>
       <c r="C85" s="26" t="s">
         <v>87</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E85" s="66">
         <v>66000</v>
       </c>
-      <c r="F85" s="206">
+      <c r="F85" s="151">
         <f t="shared" si="1"/>
         <v>59400</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="A86" s="61">
         <v>48</v>
       </c>
-      <c r="B86" s="169"/>
+      <c r="B86" s="171"/>
       <c r="C86" s="26" t="s">
         <v>150</v>
       </c>
@@ -4516,7 +4516,7 @@
       <c r="E86" s="66">
         <v>139000</v>
       </c>
-      <c r="F86" s="206">
+      <c r="F86" s="151">
         <f t="shared" si="1"/>
         <v>125100</v>
       </c>
@@ -4529,7 +4529,7 @@
       <c r="A87" s="61">
         <v>49</v>
       </c>
-      <c r="B87" s="169"/>
+      <c r="B87" s="171"/>
       <c r="C87" s="26" t="s">
         <v>152</v>
       </c>
@@ -4539,7 +4539,7 @@
       <c r="E87" s="66">
         <v>66000</v>
       </c>
-      <c r="F87" s="206">
+      <c r="F87" s="151">
         <f t="shared" si="1"/>
         <v>59400</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="A88" s="61">
         <v>50</v>
       </c>
-      <c r="B88" s="169"/>
+      <c r="B88" s="171"/>
       <c r="C88" s="26" t="s">
         <v>154</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="E88" s="66">
         <v>212000</v>
       </c>
-      <c r="F88" s="206">
+      <c r="F88" s="151">
         <f t="shared" si="1"/>
         <v>190800</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="A89" s="61">
         <v>51</v>
       </c>
-      <c r="B89" s="169"/>
+      <c r="B89" s="171"/>
       <c r="C89" s="26" t="s">
         <v>156</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="E89" s="66">
         <v>868000</v>
       </c>
-      <c r="F89" s="206">
+      <c r="F89" s="151">
         <f t="shared" si="1"/>
         <v>781200</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="A90" s="61">
         <v>52</v>
       </c>
-      <c r="B90" s="169"/>
+      <c r="B90" s="171"/>
       <c r="C90" s="26" t="s">
         <v>158</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="E90" s="66">
         <v>139000</v>
       </c>
-      <c r="F90" s="206">
+      <c r="F90" s="151">
         <f t="shared" si="1"/>
         <v>125100</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="A91" s="61">
         <v>53</v>
       </c>
-      <c r="B91" s="169"/>
+      <c r="B91" s="171"/>
       <c r="C91" s="26" t="s">
         <v>160</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="E91" s="66">
         <v>72000</v>
       </c>
-      <c r="F91" s="206">
+      <c r="F91" s="151">
         <f t="shared" si="1"/>
         <v>64800</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="A92" s="61">
         <v>54</v>
       </c>
-      <c r="B92" s="169" t="s">
+      <c r="B92" s="171" t="s">
         <v>162</v>
       </c>
       <c r="C92" s="26" t="s">
@@ -4654,7 +4654,7 @@
       <c r="E92" s="66">
         <v>174000</v>
       </c>
-      <c r="F92" s="206">
+      <c r="F92" s="151">
         <f t="shared" si="1"/>
         <v>156600</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="A93" s="61">
         <v>55</v>
       </c>
-      <c r="B93" s="169"/>
+      <c r="B93" s="171"/>
       <c r="C93" s="26" t="s">
         <v>165</v>
       </c>
@@ -4675,7 +4675,7 @@
       <c r="E93" s="66">
         <v>88000</v>
       </c>
-      <c r="F93" s="206">
+      <c r="F93" s="151">
         <f t="shared" si="1"/>
         <v>79200</v>
       </c>
@@ -4686,7 +4686,7 @@
       <c r="A94" s="61">
         <v>56</v>
       </c>
-      <c r="B94" s="169" t="s">
+      <c r="B94" s="171" t="s">
         <v>167</v>
       </c>
       <c r="C94" s="26" t="s">
@@ -4698,7 +4698,7 @@
       <c r="E94" s="62">
         <v>168000</v>
       </c>
-      <c r="F94" s="206">
+      <c r="F94" s="151">
         <f t="shared" si="1"/>
         <v>151200</v>
       </c>
@@ -4709,7 +4709,7 @@
       <c r="A95" s="61">
         <v>57</v>
       </c>
-      <c r="B95" s="169"/>
+      <c r="B95" s="171"/>
       <c r="C95" s="26" t="s">
         <v>170</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="E95" s="62">
         <v>168000</v>
       </c>
-      <c r="F95" s="206">
+      <c r="F95" s="151">
         <f t="shared" si="1"/>
         <v>151200</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="A96" s="61">
         <v>58</v>
       </c>
-      <c r="B96" s="169"/>
+      <c r="B96" s="171"/>
       <c r="C96" s="26" t="s">
         <v>172</v>
       </c>
@@ -4740,7 +4740,7 @@
       <c r="E96" s="62">
         <v>253000</v>
       </c>
-      <c r="F96" s="206">
+      <c r="F96" s="151">
         <f t="shared" si="1"/>
         <v>227700</v>
       </c>
@@ -4748,12 +4748,12 @@
       <c r="H96" s="41"/>
     </row>
     <row r="97" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="166" t="s">
+      <c r="A97" s="175" t="s">
         <v>367</v>
       </c>
-      <c r="B97" s="166"/>
-      <c r="C97" s="166"/>
-      <c r="D97" s="166"/>
+      <c r="B97" s="175"/>
+      <c r="C97" s="175"/>
+      <c r="D97" s="175"/>
       <c r="E97" s="110"/>
       <c r="F97" s="110"/>
       <c r="G97" s="126"/>
@@ -4763,7 +4763,7 @@
       <c r="A98" s="61">
         <v>59</v>
       </c>
-      <c r="B98" s="169" t="s">
+      <c r="B98" s="171" t="s">
         <v>368</v>
       </c>
       <c r="C98" s="26" t="s">
@@ -4775,7 +4775,7 @@
       <c r="E98" s="62">
         <v>250000</v>
       </c>
-      <c r="F98" s="206">
+      <c r="F98" s="151">
         <f t="shared" si="1"/>
         <v>225000</v>
       </c>
@@ -4786,7 +4786,7 @@
       <c r="A99" s="61">
         <v>60</v>
       </c>
-      <c r="B99" s="169"/>
+      <c r="B99" s="171"/>
       <c r="C99" s="26" t="s">
         <v>371</v>
       </c>
@@ -4796,7 +4796,7 @@
       <c r="E99" s="62">
         <v>399000</v>
       </c>
-      <c r="F99" s="206">
+      <c r="F99" s="151">
         <f t="shared" si="1"/>
         <v>359100</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="A100" s="61">
         <v>61</v>
       </c>
-      <c r="B100" s="169" t="s">
+      <c r="B100" s="171" t="s">
         <v>174</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4817,7 +4817,7 @@
       <c r="E100" s="62">
         <v>2500000</v>
       </c>
-      <c r="F100" s="206">
+      <c r="F100" s="151">
         <f t="shared" si="1"/>
         <v>2250000</v>
       </c>
@@ -4828,7 +4828,7 @@
       <c r="A101" s="61">
         <v>62</v>
       </c>
-      <c r="B101" s="169"/>
+      <c r="B101" s="171"/>
       <c r="C101" s="26" t="s">
         <v>176</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="E101" s="62">
         <v>2200000</v>
       </c>
-      <c r="F101" s="206">
+      <c r="F101" s="151">
         <f t="shared" si="1"/>
         <v>1980000</v>
       </c>
@@ -4857,7 +4857,7 @@
       <c r="E102" s="62">
         <v>250000</v>
       </c>
-      <c r="F102" s="206">
+      <c r="F102" s="151">
         <f t="shared" ref="F102:F143" si="2">E102*0.9</f>
         <v>225000</v>
       </c>
@@ -4870,7 +4870,7 @@
       <c r="A103" s="61">
         <v>64</v>
       </c>
-      <c r="B103" s="169" t="s">
+      <c r="B103" s="171" t="s">
         <v>179</v>
       </c>
       <c r="C103" s="26" t="s">
@@ -4880,7 +4880,7 @@
       <c r="E103" s="62">
         <v>275000</v>
       </c>
-      <c r="F103" s="206">
+      <c r="F103" s="151">
         <f t="shared" si="2"/>
         <v>247500</v>
       </c>
@@ -4891,7 +4891,7 @@
       <c r="A104" s="61">
         <v>65</v>
       </c>
-      <c r="B104" s="169"/>
+      <c r="B104" s="171"/>
       <c r="C104" s="26" t="s">
         <v>181</v>
       </c>
@@ -4899,7 +4899,7 @@
       <c r="E104" s="62">
         <v>187000</v>
       </c>
-      <c r="F104" s="206">
+      <c r="F104" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -4910,7 +4910,7 @@
       <c r="A105" s="61">
         <v>66</v>
       </c>
-      <c r="B105" s="169"/>
+      <c r="B105" s="171"/>
       <c r="C105" s="26" t="s">
         <v>182</v>
       </c>
@@ -4918,7 +4918,7 @@
       <c r="E105" s="62">
         <v>187000</v>
       </c>
-      <c r="F105" s="206">
+      <c r="F105" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -4929,7 +4929,7 @@
       <c r="A106" s="61">
         <v>67</v>
       </c>
-      <c r="B106" s="169"/>
+      <c r="B106" s="171"/>
       <c r="C106" s="26" t="s">
         <v>183</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="E106" s="62">
         <v>189000</v>
       </c>
-      <c r="F106" s="206">
+      <c r="F106" s="151">
         <f t="shared" si="2"/>
         <v>170100</v>
       </c>
@@ -4948,7 +4948,7 @@
       <c r="A107" s="61">
         <v>68</v>
       </c>
-      <c r="B107" s="169"/>
+      <c r="B107" s="171"/>
       <c r="C107" s="26" t="s">
         <v>184</v>
       </c>
@@ -4956,7 +4956,7 @@
       <c r="E107" s="62">
         <v>150000</v>
       </c>
-      <c r="F107" s="206">
+      <c r="F107" s="151">
         <f t="shared" si="2"/>
         <v>135000</v>
       </c>
@@ -4967,7 +4967,7 @@
       <c r="A108" s="61">
         <v>69</v>
       </c>
-      <c r="B108" s="169"/>
+      <c r="B108" s="171"/>
       <c r="C108" s="26" t="s">
         <v>185</v>
       </c>
@@ -4975,7 +4975,7 @@
       <c r="E108" s="62">
         <v>189000</v>
       </c>
-      <c r="F108" s="206">
+      <c r="F108" s="151">
         <f t="shared" si="2"/>
         <v>170100</v>
       </c>
@@ -4986,7 +4986,7 @@
       <c r="A109" s="61">
         <v>70</v>
       </c>
-      <c r="B109" s="169"/>
+      <c r="B109" s="171"/>
       <c r="C109" s="26" t="s">
         <v>186</v>
       </c>
@@ -4994,7 +4994,7 @@
       <c r="E109" s="62">
         <v>189000</v>
       </c>
-      <c r="F109" s="206">
+      <c r="F109" s="151">
         <f t="shared" si="2"/>
         <v>170100</v>
       </c>
@@ -5005,7 +5005,7 @@
       <c r="A110" s="61">
         <v>71</v>
       </c>
-      <c r="B110" s="169"/>
+      <c r="B110" s="171"/>
       <c r="C110" s="26" t="s">
         <v>187</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="E110" s="62">
         <v>187000</v>
       </c>
-      <c r="F110" s="206">
+      <c r="F110" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -5024,7 +5024,7 @@
       <c r="A111" s="61">
         <v>72</v>
       </c>
-      <c r="B111" s="169"/>
+      <c r="B111" s="171"/>
       <c r="C111" s="26" t="s">
         <v>188</v>
       </c>
@@ -5032,7 +5032,7 @@
       <c r="E111" s="62">
         <v>201000</v>
       </c>
-      <c r="F111" s="206">
+      <c r="F111" s="151">
         <f t="shared" si="2"/>
         <v>180900</v>
       </c>
@@ -5043,7 +5043,7 @@
       <c r="A112" s="61">
         <v>73</v>
       </c>
-      <c r="B112" s="169"/>
+      <c r="B112" s="171"/>
       <c r="C112" s="26" t="s">
         <v>189</v>
       </c>
@@ -5051,7 +5051,7 @@
       <c r="E112" s="62">
         <v>187000</v>
       </c>
-      <c r="F112" s="206">
+      <c r="F112" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -5062,7 +5062,7 @@
       <c r="A113" s="61">
         <v>74</v>
       </c>
-      <c r="B113" s="169"/>
+      <c r="B113" s="171"/>
       <c r="C113" s="26" t="s">
         <v>190</v>
       </c>
@@ -5070,7 +5070,7 @@
       <c r="E113" s="62">
         <v>187000</v>
       </c>
-      <c r="F113" s="206">
+      <c r="F113" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -5081,7 +5081,7 @@
       <c r="A114" s="61">
         <v>75</v>
       </c>
-      <c r="B114" s="169"/>
+      <c r="B114" s="171"/>
       <c r="C114" s="26" t="s">
         <v>191</v>
       </c>
@@ -5089,7 +5089,7 @@
       <c r="E114" s="62">
         <v>132000</v>
       </c>
-      <c r="F114" s="206">
+      <c r="F114" s="151">
         <f t="shared" si="2"/>
         <v>118800</v>
       </c>
@@ -5100,7 +5100,7 @@
       <c r="A115" s="61">
         <v>76</v>
       </c>
-      <c r="B115" s="169"/>
+      <c r="B115" s="171"/>
       <c r="C115" s="26" t="s">
         <v>192</v>
       </c>
@@ -5108,7 +5108,7 @@
       <c r="E115" s="62">
         <v>187000</v>
       </c>
-      <c r="F115" s="206">
+      <c r="F115" s="151">
         <f t="shared" si="2"/>
         <v>168300</v>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="A116" s="61">
         <v>77</v>
       </c>
-      <c r="B116" s="169"/>
+      <c r="B116" s="171"/>
       <c r="C116" s="26" t="s">
         <v>193</v>
       </c>
@@ -5127,7 +5127,7 @@
       <c r="E116" s="62">
         <v>1073000</v>
       </c>
-      <c r="F116" s="206">
+      <c r="F116" s="151">
         <f t="shared" si="2"/>
         <v>965700</v>
       </c>
@@ -5135,12 +5135,12 @@
       <c r="H116" s="41"/>
     </row>
     <row r="117" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="166" t="s">
+      <c r="A117" s="175" t="s">
         <v>374</v>
       </c>
-      <c r="B117" s="166"/>
-      <c r="C117" s="166"/>
-      <c r="D117" s="166"/>
+      <c r="B117" s="175"/>
+      <c r="C117" s="175"/>
+      <c r="D117" s="175"/>
       <c r="E117" s="107"/>
       <c r="F117" s="107"/>
       <c r="G117" s="126"/>
@@ -5162,7 +5162,7 @@
       <c r="E118" s="62">
         <v>50000</v>
       </c>
-      <c r="F118" s="206">
+      <c r="F118" s="151">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
@@ -5185,7 +5185,7 @@
       <c r="E119" s="62">
         <v>108000</v>
       </c>
-      <c r="F119" s="206">
+      <c r="F119" s="151">
         <f t="shared" si="2"/>
         <v>97200</v>
       </c>
@@ -5193,12 +5193,12 @@
       <c r="H119" s="41"/>
     </row>
     <row r="120" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="167" t="s">
+      <c r="A120" s="176" t="s">
         <v>381</v>
       </c>
-      <c r="B120" s="167"/>
-      <c r="C120" s="167"/>
-      <c r="D120" s="167"/>
+      <c r="B120" s="176"/>
+      <c r="C120" s="176"/>
+      <c r="D120" s="176"/>
       <c r="E120" s="108"/>
       <c r="F120" s="108"/>
       <c r="G120" s="126"/>
@@ -5208,7 +5208,7 @@
       <c r="A121" s="61">
         <v>80</v>
       </c>
-      <c r="B121" s="183" t="s">
+      <c r="B121" s="191" t="s">
         <v>382</v>
       </c>
       <c r="C121" s="26" t="s">
@@ -5220,7 +5220,7 @@
       <c r="E121" s="62">
         <v>230000</v>
       </c>
-      <c r="F121" s="207">
+      <c r="F121" s="152">
         <v>155000</v>
       </c>
       <c r="G121" s="125"/>
@@ -5230,7 +5230,7 @@
       <c r="A122" s="61">
         <v>81</v>
       </c>
-      <c r="B122" s="184"/>
+      <c r="B122" s="192"/>
       <c r="C122" s="26" t="s">
         <v>31</v>
       </c>
@@ -5240,7 +5240,7 @@
       <c r="E122" s="62">
         <v>220000</v>
       </c>
-      <c r="F122" s="207">
+      <c r="F122" s="152">
         <v>155000</v>
       </c>
       <c r="G122" s="125"/>
@@ -5250,7 +5250,7 @@
       <c r="A123" s="61">
         <v>82</v>
       </c>
-      <c r="B123" s="185"/>
+      <c r="B123" s="193"/>
       <c r="C123" s="26" t="s">
         <v>56</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="E123" s="62">
         <v>230000</v>
       </c>
-      <c r="F123" s="207">
+      <c r="F123" s="152">
         <v>155000</v>
       </c>
       <c r="G123" s="125"/>
@@ -5280,7 +5280,7 @@
       <c r="E124" s="34">
         <v>140000</v>
       </c>
-      <c r="F124" s="208">
+      <c r="F124" s="153">
         <v>70000</v>
       </c>
       <c r="G124" s="127"/>
@@ -5290,7 +5290,7 @@
       <c r="A125" s="61">
         <v>84</v>
       </c>
-      <c r="B125" s="183" t="s">
+      <c r="B125" s="191" t="s">
         <v>382</v>
       </c>
       <c r="C125" s="26" t="s">
@@ -5300,7 +5300,7 @@
       <c r="E125" s="66">
         <v>250000</v>
       </c>
-      <c r="F125" s="206">
+      <c r="F125" s="151">
         <f t="shared" si="2"/>
         <v>225000</v>
       </c>
@@ -5311,7 +5311,7 @@
       <c r="A126" s="61">
         <v>85</v>
       </c>
-      <c r="B126" s="184"/>
+      <c r="B126" s="192"/>
       <c r="C126" s="26" t="s">
         <v>384</v>
       </c>
@@ -5319,7 +5319,7 @@
       <c r="E126" s="66">
         <v>375000</v>
       </c>
-      <c r="F126" s="206">
+      <c r="F126" s="151">
         <f t="shared" si="2"/>
         <v>337500</v>
       </c>
@@ -5330,7 +5330,7 @@
       <c r="A127" s="61">
         <v>86</v>
       </c>
-      <c r="B127" s="184"/>
+      <c r="B127" s="192"/>
       <c r="C127" s="26" t="s">
         <v>194</v>
       </c>
@@ -5338,7 +5338,7 @@
       <c r="E127" s="66">
         <v>500000</v>
       </c>
-      <c r="F127" s="206">
+      <c r="F127" s="151">
         <f t="shared" si="2"/>
         <v>450000</v>
       </c>
@@ -5349,7 +5349,7 @@
       <c r="A128" s="61">
         <v>87</v>
       </c>
-      <c r="B128" s="184"/>
+      <c r="B128" s="192"/>
       <c r="C128" s="26" t="s">
         <v>195</v>
       </c>
@@ -5359,7 +5359,7 @@
       <c r="E128" s="62">
         <v>700000</v>
       </c>
-      <c r="F128" s="206">
+      <c r="F128" s="151">
         <f t="shared" si="2"/>
         <v>630000</v>
       </c>
@@ -5370,7 +5370,7 @@
       <c r="A129" s="61">
         <v>88</v>
       </c>
-      <c r="B129" s="184"/>
+      <c r="B129" s="192"/>
       <c r="C129" s="26" t="s">
         <v>197</v>
       </c>
@@ -5380,7 +5380,7 @@
       <c r="E129" s="62">
         <v>770000</v>
       </c>
-      <c r="F129" s="206">
+      <c r="F129" s="151">
         <f t="shared" si="2"/>
         <v>693000</v>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="A130" s="61">
         <v>89</v>
       </c>
-      <c r="B130" s="185"/>
+      <c r="B130" s="193"/>
       <c r="C130" s="26" t="s">
         <v>199</v>
       </c>
@@ -5401,7 +5401,7 @@
       <c r="E130" s="62">
         <v>249000</v>
       </c>
-      <c r="F130" s="206">
+      <c r="F130" s="151">
         <f t="shared" si="2"/>
         <v>224100</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="A131" s="61">
         <v>90</v>
       </c>
-      <c r="B131" s="154" t="s">
+      <c r="B131" s="199" t="s">
         <v>385</v>
       </c>
       <c r="C131" s="26" t="s">
@@ -5424,7 +5424,7 @@
       <c r="E131" s="66">
         <v>157000</v>
       </c>
-      <c r="F131" s="206">
+      <c r="F131" s="151">
         <f t="shared" si="2"/>
         <v>141300</v>
       </c>
@@ -5435,7 +5435,7 @@
       <c r="A132" s="61">
         <v>91</v>
       </c>
-      <c r="B132" s="155"/>
+      <c r="B132" s="200"/>
       <c r="C132" s="26" t="s">
         <v>201</v>
       </c>
@@ -5445,7 +5445,7 @@
       <c r="E132" s="66">
         <v>157000</v>
       </c>
-      <c r="F132" s="206">
+      <c r="F132" s="151">
         <f t="shared" si="2"/>
         <v>141300</v>
       </c>
@@ -5456,7 +5456,7 @@
       <c r="A133" s="61">
         <v>92</v>
       </c>
-      <c r="B133" s="155"/>
+      <c r="B133" s="200"/>
       <c r="C133" s="26" t="s">
         <v>203</v>
       </c>
@@ -5466,7 +5466,7 @@
       <c r="E133" s="66">
         <v>143000</v>
       </c>
-      <c r="F133" s="206">
+      <c r="F133" s="151">
         <f t="shared" si="2"/>
         <v>128700</v>
       </c>
@@ -5477,7 +5477,7 @@
       <c r="A134" s="61">
         <v>93</v>
       </c>
-      <c r="B134" s="156"/>
+      <c r="B134" s="201"/>
       <c r="C134" s="26" t="s">
         <v>205</v>
       </c>
@@ -5487,7 +5487,7 @@
       <c r="E134" s="66">
         <v>185000</v>
       </c>
-      <c r="F134" s="206">
+      <c r="F134" s="151">
         <f t="shared" si="2"/>
         <v>166500</v>
       </c>
@@ -5498,7 +5498,7 @@
       <c r="A135" s="61">
         <v>94</v>
       </c>
-      <c r="B135" s="154" t="s">
+      <c r="B135" s="199" t="s">
         <v>419</v>
       </c>
       <c r="C135" s="133" t="s">
@@ -5510,7 +5510,7 @@
       <c r="E135" s="134">
         <v>1200000</v>
       </c>
-      <c r="F135" s="209">
+      <c r="F135" s="154">
         <f t="shared" si="2"/>
         <v>1080000</v>
       </c>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="136" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A136" s="61"/>
-      <c r="B136" s="155"/>
+      <c r="B136" s="200"/>
       <c r="C136" s="133" t="s">
         <v>421</v>
       </c>
@@ -5527,7 +5527,7 @@
       <c r="E136" s="134">
         <v>200000</v>
       </c>
-      <c r="F136" s="209">
+      <c r="F136" s="154">
         <f t="shared" si="2"/>
         <v>180000</v>
       </c>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="137" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A137" s="61"/>
-      <c r="B137" s="155"/>
+      <c r="B137" s="200"/>
       <c r="C137" s="133" t="s">
         <v>420</v>
       </c>
@@ -5544,7 +5544,7 @@
       <c r="E137" s="134">
         <v>300000</v>
       </c>
-      <c r="F137" s="209">
+      <c r="F137" s="154">
         <f t="shared" si="2"/>
         <v>270000</v>
       </c>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="138" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A138" s="61"/>
-      <c r="B138" s="155"/>
+      <c r="B138" s="200"/>
       <c r="C138" s="133" t="s">
         <v>422</v>
       </c>
@@ -5561,7 +5561,7 @@
       <c r="E138" s="134">
         <v>600000</v>
       </c>
-      <c r="F138" s="209">
+      <c r="F138" s="154">
         <f t="shared" si="2"/>
         <v>540000</v>
       </c>
@@ -5572,7 +5572,7 @@
       <c r="A139" s="61">
         <v>95</v>
       </c>
-      <c r="B139" s="168"/>
+      <c r="B139" s="164"/>
       <c r="C139" s="26" t="s">
         <v>208</v>
       </c>
@@ -5582,7 +5582,7 @@
       <c r="E139" s="66">
         <v>700000</v>
       </c>
-      <c r="F139" s="206">
+      <c r="F139" s="151">
         <f t="shared" si="2"/>
         <v>630000</v>
       </c>
@@ -5593,7 +5593,7 @@
       <c r="A140" s="61">
         <v>96</v>
       </c>
-      <c r="B140" s="168"/>
+      <c r="B140" s="164"/>
       <c r="C140" s="26" t="s">
         <v>210</v>
       </c>
@@ -5603,7 +5603,7 @@
       <c r="E140" s="62">
         <v>847000</v>
       </c>
-      <c r="F140" s="206">
+      <c r="F140" s="151">
         <f t="shared" si="2"/>
         <v>762300</v>
       </c>
@@ -5614,7 +5614,7 @@
       <c r="A141" s="61">
         <v>97</v>
       </c>
-      <c r="B141" s="168"/>
+      <c r="B141" s="164"/>
       <c r="C141" s="26" t="s">
         <v>212</v>
       </c>
@@ -5624,7 +5624,7 @@
       <c r="E141" s="62">
         <v>2178000</v>
       </c>
-      <c r="F141" s="206">
+      <c r="F141" s="151">
         <f t="shared" si="2"/>
         <v>1960200</v>
       </c>
@@ -5635,7 +5635,7 @@
       <c r="A142" s="61">
         <v>98</v>
       </c>
-      <c r="B142" s="168"/>
+      <c r="B142" s="164"/>
       <c r="C142" s="26" t="s">
         <v>214</v>
       </c>
@@ -5645,7 +5645,7 @@
       <c r="E142" s="62">
         <v>847000</v>
       </c>
-      <c r="F142" s="206">
+      <c r="F142" s="151">
         <f t="shared" si="2"/>
         <v>762300</v>
       </c>
@@ -5656,7 +5656,7 @@
       <c r="A143" s="61">
         <v>99</v>
       </c>
-      <c r="B143" s="168"/>
+      <c r="B143" s="164"/>
       <c r="C143" s="26" t="s">
         <v>216</v>
       </c>
@@ -5666,7 +5666,7 @@
       <c r="E143" s="62">
         <v>1700000</v>
       </c>
-      <c r="F143" s="206">
+      <c r="F143" s="151">
         <f t="shared" si="2"/>
         <v>1530000</v>
       </c>
@@ -5677,7 +5677,7 @@
       <c r="A144" s="61">
         <v>100</v>
       </c>
-      <c r="B144" s="168" t="s">
+      <c r="B144" s="164" t="s">
         <v>386</v>
       </c>
       <c r="C144" s="26" t="s">
@@ -5699,7 +5699,7 @@
       <c r="A145" s="61">
         <v>101</v>
       </c>
-      <c r="B145" s="168"/>
+      <c r="B145" s="164"/>
       <c r="C145" s="26" t="s">
         <v>220</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="A146" s="61">
         <v>102</v>
       </c>
-      <c r="B146" s="168"/>
+      <c r="B146" s="164"/>
       <c r="C146" s="26" t="s">
         <v>222</v>
       </c>
@@ -5742,7 +5742,7 @@
       <c r="A147" s="61">
         <v>103</v>
       </c>
-      <c r="B147" s="168"/>
+      <c r="B147" s="164"/>
       <c r="C147" s="26" t="s">
         <v>224</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="A148" s="61">
         <v>104</v>
       </c>
-      <c r="B148" s="168"/>
+      <c r="B148" s="164"/>
       <c r="C148" s="26" t="s">
         <v>226</v>
       </c>
@@ -5782,7 +5782,7 @@
       <c r="A149" s="61">
         <v>105</v>
       </c>
-      <c r="B149" s="168"/>
+      <c r="B149" s="164"/>
       <c r="C149" s="26" t="s">
         <v>228</v>
       </c>
@@ -5802,7 +5802,7 @@
       <c r="A150" s="61">
         <v>106</v>
       </c>
-      <c r="B150" s="168"/>
+      <c r="B150" s="164"/>
       <c r="C150" s="26" t="s">
         <v>414</v>
       </c>
@@ -5822,7 +5822,7 @@
       <c r="A151" s="61">
         <v>107</v>
       </c>
-      <c r="B151" s="168"/>
+      <c r="B151" s="164"/>
       <c r="C151" s="26" t="s">
         <v>231</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="A152" s="61">
         <v>108</v>
       </c>
-      <c r="B152" s="168"/>
+      <c r="B152" s="164"/>
       <c r="C152" s="26" t="s">
         <v>232</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="A153" s="61">
         <v>109</v>
       </c>
-      <c r="B153" s="168"/>
+      <c r="B153" s="164"/>
       <c r="C153" s="26" t="s">
         <v>234</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="A154" s="61">
         <v>110</v>
       </c>
-      <c r="B154" s="168"/>
+      <c r="B154" s="164"/>
       <c r="C154" s="26" t="s">
         <v>236</v>
       </c>
@@ -5904,7 +5904,7 @@
       <c r="A155" s="61">
         <v>111</v>
       </c>
-      <c r="B155" s="168"/>
+      <c r="B155" s="164"/>
       <c r="C155" s="26" t="s">
         <v>238</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="A156" s="61">
         <v>112</v>
       </c>
-      <c r="B156" s="168"/>
+      <c r="B156" s="164"/>
       <c r="C156" s="26" t="s">
         <v>240</v>
       </c>
@@ -5944,7 +5944,7 @@
       <c r="A157" s="61">
         <v>113</v>
       </c>
-      <c r="B157" s="168"/>
+      <c r="B157" s="164"/>
       <c r="C157" s="26" t="s">
         <v>241</v>
       </c>
@@ -5964,7 +5964,7 @@
       <c r="A158" s="61">
         <v>114</v>
       </c>
-      <c r="B158" s="168"/>
+      <c r="B158" s="164"/>
       <c r="C158" s="26" t="s">
         <v>243</v>
       </c>
@@ -5984,7 +5984,7 @@
       <c r="A159" s="61">
         <v>115</v>
       </c>
-      <c r="B159" s="168"/>
+      <c r="B159" s="164"/>
       <c r="C159" s="26" t="s">
         <v>244</v>
       </c>
@@ -6004,7 +6004,7 @@
       <c r="A160" s="61">
         <v>116</v>
       </c>
-      <c r="B160" s="168"/>
+      <c r="B160" s="164"/>
       <c r="C160" s="26" t="s">
         <v>246</v>
       </c>
@@ -6024,7 +6024,7 @@
       <c r="A161" s="61">
         <v>117</v>
       </c>
-      <c r="B161" s="168"/>
+      <c r="B161" s="164"/>
       <c r="C161" s="26" t="s">
         <v>248</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="A162" s="61">
         <v>118</v>
       </c>
-      <c r="B162" s="168"/>
+      <c r="B162" s="164"/>
       <c r="C162" s="26" t="s">
         <v>250</v>
       </c>
@@ -6064,7 +6064,7 @@
       <c r="A163" s="61">
         <v>119</v>
       </c>
-      <c r="B163" s="168"/>
+      <c r="B163" s="164"/>
       <c r="C163" s="26" t="s">
         <v>252</v>
       </c>
@@ -6084,7 +6084,7 @@
       <c r="A164" s="61">
         <v>120</v>
       </c>
-      <c r="B164" s="168"/>
+      <c r="B164" s="164"/>
       <c r="C164" s="26" t="s">
         <v>254</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="A165" s="61">
         <v>121</v>
       </c>
-      <c r="B165" s="168"/>
+      <c r="B165" s="164"/>
       <c r="C165" s="26" t="s">
         <v>256</v>
       </c>
@@ -6124,7 +6124,7 @@
       <c r="A166" s="61">
         <v>122</v>
       </c>
-      <c r="B166" s="168"/>
+      <c r="B166" s="164"/>
       <c r="C166" s="26" t="s">
         <v>258</v>
       </c>
@@ -6144,7 +6144,7 @@
       <c r="A167" s="61">
         <v>123</v>
       </c>
-      <c r="B167" s="168"/>
+      <c r="B167" s="164"/>
       <c r="C167" s="26" t="s">
         <v>260</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="A168" s="61">
         <v>124</v>
       </c>
-      <c r="B168" s="168"/>
+      <c r="B168" s="164"/>
       <c r="C168" s="26" t="s">
         <v>262</v>
       </c>
@@ -6182,7 +6182,7 @@
       <c r="A169" s="61">
         <v>125</v>
       </c>
-      <c r="B169" s="168"/>
+      <c r="B169" s="164"/>
       <c r="C169" s="26" t="s">
         <v>263</v>
       </c>
@@ -6200,7 +6200,7 @@
       <c r="A170" s="61">
         <v>126</v>
       </c>
-      <c r="B170" s="168"/>
+      <c r="B170" s="164"/>
       <c r="C170" s="26" t="s">
         <v>264</v>
       </c>
@@ -6220,7 +6220,7 @@
       <c r="A171" s="61">
         <v>127</v>
       </c>
-      <c r="B171" s="168"/>
+      <c r="B171" s="164"/>
       <c r="C171" s="26" t="s">
         <v>266</v>
       </c>
@@ -6240,7 +6240,7 @@
       <c r="A172" s="61">
         <v>128</v>
       </c>
-      <c r="B172" s="168"/>
+      <c r="B172" s="164"/>
       <c r="C172" s="26" t="s">
         <v>268</v>
       </c>
@@ -6260,7 +6260,7 @@
       <c r="A173" s="61">
         <v>129</v>
       </c>
-      <c r="B173" s="168"/>
+      <c r="B173" s="164"/>
       <c r="C173" s="26" t="s">
         <v>270</v>
       </c>
@@ -6277,12 +6277,12 @@
       <c r="H173" s="41"/>
     </row>
     <row r="174" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A174" s="167" t="s">
+      <c r="A174" s="176" t="s">
         <v>388</v>
       </c>
-      <c r="B174" s="167"/>
-      <c r="C174" s="167"/>
-      <c r="D174" s="167"/>
+      <c r="B174" s="176"/>
+      <c r="C174" s="176"/>
+      <c r="D174" s="176"/>
       <c r="E174" s="108"/>
       <c r="F174" s="108"/>
       <c r="G174" s="126"/>
@@ -6302,7 +6302,7 @@
       <c r="E175" s="66">
         <v>88000</v>
       </c>
-      <c r="F175" s="206">
+      <c r="F175" s="151">
         <f t="shared" ref="F175:F212" si="3">E175*0.9</f>
         <v>79200</v>
       </c>
@@ -6323,7 +6323,7 @@
       <c r="E176" s="66">
         <v>450000</v>
       </c>
-      <c r="F176" s="206">
+      <c r="F176" s="151">
         <f t="shared" si="3"/>
         <v>405000</v>
       </c>
@@ -6334,7 +6334,7 @@
       <c r="A177" s="61">
         <v>132</v>
       </c>
-      <c r="B177" s="168" t="s">
+      <c r="B177" s="164" t="s">
         <v>389</v>
       </c>
       <c r="C177" s="26" t="s">
@@ -6346,7 +6346,7 @@
       <c r="E177" s="66">
         <v>178000</v>
       </c>
-      <c r="F177" s="206">
+      <c r="F177" s="151">
         <f t="shared" si="3"/>
         <v>160200</v>
       </c>
@@ -6356,7 +6356,7 @@
       <c r="A178" s="61">
         <v>133</v>
       </c>
-      <c r="B178" s="168"/>
+      <c r="B178" s="164"/>
       <c r="C178" s="26" t="s">
         <v>392</v>
       </c>
@@ -6366,19 +6366,19 @@
       <c r="E178" s="66">
         <v>127000</v>
       </c>
-      <c r="F178" s="206">
+      <c r="F178" s="151">
         <f t="shared" si="3"/>
         <v>114300</v>
       </c>
       <c r="G178" s="125"/>
     </row>
     <row r="179" spans="1:8" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="166" t="s">
+      <c r="A179" s="175" t="s">
         <v>394</v>
       </c>
-      <c r="B179" s="166"/>
-      <c r="C179" s="166"/>
-      <c r="D179" s="166"/>
+      <c r="B179" s="175"/>
+      <c r="C179" s="175"/>
+      <c r="D179" s="175"/>
       <c r="E179" s="52"/>
       <c r="F179" s="52"/>
       <c r="G179" s="111"/>
@@ -6397,11 +6397,11 @@
       <c r="E180" s="72">
         <v>71000</v>
       </c>
-      <c r="F180" s="206">
+      <c r="F180" s="151">
         <f t="shared" si="3"/>
         <v>63900</v>
       </c>
-      <c r="G180" s="187" t="s">
+      <c r="G180" s="195" t="s">
         <v>395</v>
       </c>
     </row>
@@ -6419,19 +6419,19 @@
       <c r="E181" s="72">
         <v>86000</v>
       </c>
-      <c r="F181" s="206">
+      <c r="F181" s="151">
         <f t="shared" si="3"/>
         <v>77400</v>
       </c>
-      <c r="G181" s="187"/>
+      <c r="G181" s="195"/>
     </row>
     <row r="182" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="167" t="s">
+      <c r="A182" s="176" t="s">
         <v>396</v>
       </c>
-      <c r="B182" s="167"/>
-      <c r="C182" s="167"/>
-      <c r="D182" s="167"/>
+      <c r="B182" s="176"/>
+      <c r="C182" s="176"/>
+      <c r="D182" s="176"/>
       <c r="E182" s="108"/>
       <c r="F182" s="108"/>
       <c r="G182" s="126"/>
@@ -6451,11 +6451,11 @@
       <c r="E183" s="66">
         <v>1968000</v>
       </c>
-      <c r="F183" s="206">
+      <c r="F183" s="151">
         <f t="shared" si="3"/>
         <v>1771200</v>
       </c>
-      <c r="G183" s="168" t="s">
+      <c r="G183" s="164" t="s">
         <v>413</v>
       </c>
       <c r="H183" s="41"/>
@@ -6474,11 +6474,11 @@
       <c r="E184" s="66">
         <v>2952000</v>
       </c>
-      <c r="F184" s="206">
+      <c r="F184" s="151">
         <f t="shared" si="3"/>
         <v>2656800</v>
       </c>
-      <c r="G184" s="168"/>
+      <c r="G184" s="164"/>
       <c r="H184" s="41"/>
     </row>
     <row r="185" spans="1:8" ht="82.5" x14ac:dyDescent="0.25">
@@ -6495,11 +6495,11 @@
       <c r="E185" s="66">
         <v>4100000</v>
       </c>
-      <c r="F185" s="206">
+      <c r="F185" s="151">
         <f t="shared" si="3"/>
         <v>3690000</v>
       </c>
-      <c r="G185" s="168"/>
+      <c r="G185" s="164"/>
       <c r="H185" s="41"/>
     </row>
     <row r="186" spans="1:8" ht="66" x14ac:dyDescent="0.25">
@@ -6516,7 +6516,7 @@
       <c r="E186" s="66">
         <v>550000</v>
       </c>
-      <c r="F186" s="206">
+      <c r="F186" s="151">
         <f t="shared" si="3"/>
         <v>495000</v>
       </c>
@@ -6537,7 +6537,7 @@
       <c r="E187" s="66">
         <v>495000</v>
       </c>
-      <c r="F187" s="206">
+      <c r="F187" s="151">
         <f t="shared" si="3"/>
         <v>445500</v>
       </c>
@@ -6560,7 +6560,7 @@
       <c r="E188" s="66">
         <v>268000</v>
       </c>
-      <c r="F188" s="206">
+      <c r="F188" s="151">
         <f t="shared" si="3"/>
         <v>241200</v>
       </c>
@@ -6581,7 +6581,7 @@
       <c r="E189" s="66">
         <v>151000</v>
       </c>
-      <c r="F189" s="206">
+      <c r="F189" s="151">
         <f t="shared" si="3"/>
         <v>135900</v>
       </c>
@@ -6602,7 +6602,7 @@
       <c r="E190" s="66">
         <v>220000</v>
       </c>
-      <c r="F190" s="206">
+      <c r="F190" s="151">
         <f t="shared" si="3"/>
         <v>198000</v>
       </c>
@@ -6610,12 +6610,12 @@
       <c r="H190" s="41"/>
     </row>
     <row r="191" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A191" s="167" t="s">
+      <c r="A191" s="176" t="s">
         <v>398</v>
       </c>
-      <c r="B191" s="167"/>
-      <c r="C191" s="167"/>
-      <c r="D191" s="167"/>
+      <c r="B191" s="176"/>
+      <c r="C191" s="176"/>
+      <c r="D191" s="176"/>
       <c r="E191" s="108"/>
       <c r="F191" s="108"/>
       <c r="G191" s="126"/>
@@ -6635,7 +6635,7 @@
       <c r="E192" s="66">
         <v>390000</v>
       </c>
-      <c r="F192" s="206">
+      <c r="F192" s="151">
         <f t="shared" si="3"/>
         <v>351000</v>
       </c>
@@ -6643,12 +6643,12 @@
       <c r="H192" s="41"/>
     </row>
     <row r="193" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A193" s="167" t="s">
+      <c r="A193" s="176" t="s">
         <v>399</v>
       </c>
-      <c r="B193" s="167"/>
-      <c r="C193" s="167"/>
-      <c r="D193" s="167"/>
+      <c r="B193" s="176"/>
+      <c r="C193" s="176"/>
+      <c r="D193" s="176"/>
       <c r="E193" s="108"/>
       <c r="F193" s="108"/>
       <c r="G193" s="126"/>
@@ -6668,7 +6668,7 @@
       <c r="E194" s="62">
         <v>165000</v>
       </c>
-      <c r="F194" s="206" t="s">
+      <c r="F194" s="151" t="s">
         <v>331</v>
       </c>
       <c r="G194" s="125"/>
@@ -6688,7 +6688,7 @@
       <c r="E195" s="62">
         <v>72000</v>
       </c>
-      <c r="F195" s="206">
+      <c r="F195" s="151">
         <f t="shared" si="3"/>
         <v>64800</v>
       </c>
@@ -6709,7 +6709,7 @@
       <c r="E196" s="62">
         <v>329000</v>
       </c>
-      <c r="F196" s="206">
+      <c r="F196" s="151">
         <f t="shared" si="3"/>
         <v>296100</v>
       </c>
@@ -6730,7 +6730,7 @@
       <c r="E197" s="62">
         <v>605000</v>
       </c>
-      <c r="F197" s="206">
+      <c r="F197" s="151">
         <f t="shared" si="3"/>
         <v>544500</v>
       </c>
@@ -6751,7 +6751,7 @@
       <c r="E198" s="62">
         <v>1100000</v>
       </c>
-      <c r="F198" s="206">
+      <c r="F198" s="151">
         <f t="shared" si="3"/>
         <v>990000</v>
       </c>
@@ -6772,7 +6772,7 @@
       <c r="E199" s="62">
         <v>187000</v>
       </c>
-      <c r="F199" s="206">
+      <c r="F199" s="151">
         <f t="shared" si="3"/>
         <v>168300</v>
       </c>
@@ -6793,7 +6793,7 @@
       <c r="E200" s="62">
         <v>220000</v>
       </c>
-      <c r="F200" s="206">
+      <c r="F200" s="151">
         <f t="shared" si="3"/>
         <v>198000</v>
       </c>
@@ -6814,7 +6814,7 @@
       <c r="E201" s="62">
         <v>817000</v>
       </c>
-      <c r="F201" s="206">
+      <c r="F201" s="151">
         <f t="shared" si="3"/>
         <v>735300</v>
       </c>
@@ -6835,7 +6835,7 @@
       <c r="E202" s="66">
         <v>220000</v>
       </c>
-      <c r="F202" s="206">
+      <c r="F202" s="151">
         <f t="shared" si="3"/>
         <v>198000</v>
       </c>
@@ -6843,12 +6843,12 @@
       <c r="H202" s="41"/>
     </row>
     <row r="203" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="166" t="s">
+      <c r="A203" s="175" t="s">
         <v>404</v>
       </c>
-      <c r="B203" s="166"/>
-      <c r="C203" s="166"/>
-      <c r="D203" s="166"/>
+      <c r="B203" s="175"/>
+      <c r="C203" s="175"/>
+      <c r="D203" s="175"/>
       <c r="E203" s="107"/>
       <c r="F203" s="107"/>
       <c r="G203" s="126"/>
@@ -6866,7 +6866,7 @@
       <c r="E204" s="66">
         <v>165000</v>
       </c>
-      <c r="F204" s="206">
+      <c r="F204" s="151">
         <f t="shared" si="3"/>
         <v>148500</v>
       </c>
@@ -6887,7 +6887,7 @@
       <c r="E205" s="66">
         <v>220000</v>
       </c>
-      <c r="F205" s="206">
+      <c r="F205" s="151">
         <f t="shared" si="3"/>
         <v>198000</v>
       </c>
@@ -6908,7 +6908,7 @@
       <c r="E206" s="66">
         <v>380000</v>
       </c>
-      <c r="F206" s="206">
+      <c r="F206" s="151">
         <f t="shared" si="3"/>
         <v>342000</v>
       </c>
@@ -6956,12 +6956,12 @@
       <c r="H208" s="41"/>
     </row>
     <row r="209" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A209" s="166" t="s">
+      <c r="A209" s="175" t="s">
         <v>406</v>
       </c>
-      <c r="B209" s="166"/>
-      <c r="C209" s="166"/>
-      <c r="D209" s="166"/>
+      <c r="B209" s="175"/>
+      <c r="C209" s="175"/>
+      <c r="D209" s="175"/>
       <c r="E209" s="107"/>
       <c r="F209" s="107"/>
       <c r="G209" s="126"/>
@@ -6981,7 +6981,7 @@
       <c r="E210" s="74">
         <v>233000</v>
       </c>
-      <c r="F210" s="206">
+      <c r="F210" s="151">
         <f t="shared" si="3"/>
         <v>209700</v>
       </c>
@@ -7002,7 +7002,7 @@
       <c r="E211" s="76">
         <v>227000</v>
       </c>
-      <c r="F211" s="206">
+      <c r="F211" s="151">
         <f t="shared" si="3"/>
         <v>204300</v>
       </c>
@@ -7023,7 +7023,7 @@
       <c r="E212" s="76">
         <v>72000</v>
       </c>
-      <c r="F212" s="206">
+      <c r="F212" s="151">
         <f t="shared" si="3"/>
         <v>64800</v>
       </c>
@@ -7031,32 +7031,32 @@
       <c r="H212" s="41"/>
     </row>
     <row r="213" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A213" s="166" t="s">
+      <c r="A213" s="175" t="s">
         <v>407</v>
       </c>
-      <c r="B213" s="166"/>
-      <c r="C213" s="166"/>
-      <c r="D213" s="166"/>
+      <c r="B213" s="175"/>
+      <c r="C213" s="175"/>
+      <c r="D213" s="175"/>
       <c r="E213" s="104"/>
       <c r="F213" s="104"/>
       <c r="G213" s="126"/>
       <c r="H213" s="105"/>
     </row>
     <row r="214" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="151">
+      <c r="A214" s="196">
         <v>162</v>
       </c>
-      <c r="B214" s="154" t="s">
+      <c r="B214" s="199" t="s">
         <v>417</v>
       </c>
       <c r="C214" s="26" t="s">
         <v>322</v>
       </c>
       <c r="D214" s="26"/>
-      <c r="E214" s="186">
+      <c r="E214" s="194">
         <v>183000</v>
       </c>
-      <c r="F214" s="210">
+      <c r="F214" s="190">
         <f>E214*0.9</f>
         <v>164700</v>
       </c>
@@ -7064,48 +7064,48 @@
       <c r="H214" s="41"/>
     </row>
     <row r="215" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A215" s="152"/>
-      <c r="B215" s="155"/>
+      <c r="A215" s="197"/>
+      <c r="B215" s="200"/>
       <c r="C215" s="26" t="s">
         <v>323</v>
       </c>
       <c r="D215" s="26"/>
-      <c r="E215" s="186"/>
-      <c r="F215" s="210"/>
+      <c r="E215" s="194"/>
+      <c r="F215" s="190"/>
       <c r="G215" s="125"/>
       <c r="H215" s="41"/>
     </row>
     <row r="216" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="152"/>
-      <c r="B216" s="155"/>
+      <c r="A216" s="197"/>
+      <c r="B216" s="200"/>
       <c r="C216" s="26" t="s">
         <v>324</v>
       </c>
       <c r="D216" s="26"/>
-      <c r="E216" s="186"/>
-      <c r="F216" s="210"/>
+      <c r="E216" s="194"/>
+      <c r="F216" s="190"/>
       <c r="G216" s="125"/>
       <c r="H216" s="41"/>
     </row>
     <row r="217" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A217" s="153"/>
-      <c r="B217" s="156"/>
+      <c r="A217" s="198"/>
+      <c r="B217" s="201"/>
       <c r="C217" s="26" t="s">
         <v>325</v>
       </c>
       <c r="D217" s="26"/>
-      <c r="E217" s="186"/>
-      <c r="F217" s="210"/>
+      <c r="E217" s="194"/>
+      <c r="F217" s="190"/>
       <c r="G217" s="125"/>
       <c r="H217" s="41"/>
     </row>
     <row r="218" spans="1:8" s="106" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A218" s="166" t="s">
+      <c r="A218" s="175" t="s">
         <v>408</v>
       </c>
-      <c r="B218" s="166"/>
-      <c r="C218" s="166"/>
-      <c r="D218" s="166"/>
+      <c r="B218" s="175"/>
+      <c r="C218" s="175"/>
+      <c r="D218" s="175"/>
       <c r="E218" s="104"/>
       <c r="F218" s="104"/>
       <c r="G218" s="126"/>
@@ -7197,22 +7197,22 @@
       <c r="B224" s="147"/>
       <c r="C224" s="100"/>
       <c r="D224" s="100"/>
-      <c r="E224" s="204" t="s">
+      <c r="E224" s="155" t="s">
         <v>334</v>
       </c>
-      <c r="F224" s="204"/>
-      <c r="G224" s="204"/>
+      <c r="F224" s="155"/>
+      <c r="G224" s="155"/>
     </row>
     <row r="225" spans="1:7" s="53" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="88"/>
       <c r="B225" s="147"/>
       <c r="C225" s="100"/>
       <c r="D225" s="100"/>
-      <c r="E225" s="205" t="s">
+      <c r="E225" s="156" t="s">
         <v>423</v>
       </c>
-      <c r="F225" s="205"/>
-      <c r="G225" s="205"/>
+      <c r="F225" s="156"/>
+      <c r="G225" s="156"/>
     </row>
     <row r="226" spans="1:7" s="53" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A226" s="88"/>
@@ -7332,69 +7332,69 @@
       <c r="G238" s="129"/>
     </row>
     <row r="239" spans="1:7" s="103" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="193" t="s">
+      <c r="A239" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="B239" s="193"/>
-      <c r="C239" s="193"/>
-      <c r="D239" s="193"/>
+      <c r="B239" s="169"/>
+      <c r="C239" s="169"/>
+      <c r="D239" s="169"/>
       <c r="E239" s="102"/>
       <c r="F239" s="102"/>
       <c r="G239" s="130"/>
     </row>
     <row r="240" spans="1:7" s="83" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A240" s="84"/>
-      <c r="B240" s="192" t="s">
+      <c r="B240" s="168" t="s">
         <v>54</v>
       </c>
-      <c r="C240" s="192"/>
-      <c r="D240" s="192"/>
-      <c r="E240" s="192"/>
-      <c r="F240" s="192"/>
+      <c r="C240" s="168"/>
+      <c r="D240" s="168"/>
+      <c r="E240" s="168"/>
+      <c r="F240" s="168"/>
       <c r="G240" s="86"/>
     </row>
     <row r="241" spans="1:7" s="83" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A241" s="84"/>
-      <c r="B241" s="192" t="s">
+      <c r="B241" s="168" t="s">
         <v>335</v>
       </c>
-      <c r="C241" s="192"/>
-      <c r="D241" s="192"/>
-      <c r="E241" s="192"/>
-      <c r="F241" s="192"/>
+      <c r="C241" s="168"/>
+      <c r="D241" s="168"/>
+      <c r="E241" s="168"/>
+      <c r="F241" s="168"/>
       <c r="G241" s="86"/>
     </row>
     <row r="242" spans="1:7" s="87" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="85"/>
-      <c r="B242" s="198" t="s">
+      <c r="B242" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="C242" s="198"/>
-      <c r="D242" s="198"/>
-      <c r="E242" s="198"/>
-      <c r="F242" s="198"/>
-      <c r="G242" s="198"/>
+      <c r="C242" s="174"/>
+      <c r="D242" s="174"/>
+      <c r="E242" s="174"/>
+      <c r="F242" s="174"/>
+      <c r="G242" s="174"/>
     </row>
     <row r="243" spans="1:7" s="89" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="88"/>
-      <c r="B243" s="197" t="s">
+      <c r="B243" s="173" t="s">
         <v>26</v>
       </c>
-      <c r="C243" s="197"/>
-      <c r="D243" s="197"/>
-      <c r="E243" s="197"/>
-      <c r="F243" s="197"/>
-      <c r="G243" s="197"/>
+      <c r="C243" s="173"/>
+      <c r="D243" s="173"/>
+      <c r="E243" s="173"/>
+      <c r="F243" s="173"/>
+      <c r="G243" s="173"/>
     </row>
     <row r="244" spans="1:7" s="90" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A244" s="88"/>
-      <c r="B244" s="192" t="s">
+      <c r="B244" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="C244" s="192"/>
-      <c r="D244" s="192"/>
-      <c r="E244" s="192"/>
-      <c r="F244" s="192"/>
+      <c r="C244" s="168"/>
+      <c r="D244" s="168"/>
+      <c r="E244" s="168"/>
+      <c r="F244" s="168"/>
       <c r="G244" s="86"/>
     </row>
     <row r="245" spans="1:7" s="90" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -7519,49 +7519,22 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="E224:G224"/>
-    <mergeCell ref="E225:G225"/>
-    <mergeCell ref="F15:F20"/>
-    <mergeCell ref="E15:E20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="A239:D239"/>
-    <mergeCell ref="B240:F240"/>
-    <mergeCell ref="B241:F241"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="B243:G243"/>
-    <mergeCell ref="B242:G242"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="B63:B75"/>
-    <mergeCell ref="B79:B82"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A214:A217"/>
+    <mergeCell ref="B214:B217"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="A218:D218"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="B139:B143"/>
+    <mergeCell ref="B144:B173"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="B103:B116"/>
+    <mergeCell ref="B131:B134"/>
+    <mergeCell ref="B135:B138"/>
+    <mergeCell ref="G76:G78"/>
     <mergeCell ref="D1:G5"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="A7:G7"/>
@@ -7578,29 +7551,56 @@
     <mergeCell ref="G183:G185"/>
     <mergeCell ref="A191:D191"/>
     <mergeCell ref="A193:D193"/>
-    <mergeCell ref="A214:A217"/>
-    <mergeCell ref="B214:B217"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G11"/>
-    <mergeCell ref="A218:D218"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="B139:B143"/>
-    <mergeCell ref="B144:B173"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="B103:B116"/>
-    <mergeCell ref="B131:B134"/>
-    <mergeCell ref="B135:B138"/>
-    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="B84:B91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="B63:B75"/>
+    <mergeCell ref="B79:B82"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="A239:D239"/>
+    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="B241:F241"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="B243:G243"/>
+    <mergeCell ref="B242:G242"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="E224:G224"/>
+    <mergeCell ref="E225:G225"/>
+    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="E15:E20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="G60:G61"/>
   </mergeCells>
   <conditionalFormatting sqref="C124">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.25" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="57" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>